--- a/wooclap/imports/optional/08_Intro_ML_Part_2_optional.xlsx
+++ b/wooclap/imports/optional/08_Intro_ML_Part_2_optional.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$3</definedName>

--- a/wooclap/imports/optional/08_Intro_ML_Part_2_optional.xlsx
+++ b/wooclap/imports/optional/08_Intro_ML_Part_2_optional.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L03-O02 · Which is a setting you choose before fitting a polynomial model, rather than a coefficient learned during fitting?</t>
+          <t>L03-O02 · We choose the family fθ(x)=ax²+bx+c, then fitting changes θ from (1,0,0) to (2,−1,0.5). What changed?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The fitted intercept.</t>
+          <t>The family changed from quadratic to cubic.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The fitted coefficient of x.</t>
+          <t>The polynomial degree was learned, but the coefficients stayed fixed.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The fitted coefficient of x squared.</t>
+          <t>A new parameter space was required because a coefficient became negative.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The polynomial degree: for example, choosing a line or a quadratic curve.</t>
+          <t>The parameter setting changed within the same Θ=ℝ³; allowing a different degree would change the family.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L03-O03 · You want to predict next month’s sales. Which test best resembles that use?</t>
+          <t>L03-O03 · Deployment will predict future months for fields not used in training. The dataset has repeated monthly rows for each field. Which held-out evaluation matches both requirements?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Learn from next month’s actual sales before predicting them.</t>
+          <t>Randomly shuffle individual rows so the same fields and future dates can appear in training.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Learn from earlier months and test on a later month.</t>
+          <t>Train on earlier data from one group of fields, then evaluate later data from different fields.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Report only how well the model fits its training months.</t>
+          <t>Hold out later months but keep exactly the same fields in training and evaluation.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Include the answer for each test month among its inputs.</t>
+          <t>Hold out field identities but allow later measurements to enter training before predicting earlier dates.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>

--- a/wooclap/imports/optional/08_Intro_ML_Part_2_optional.xlsx
+++ b/wooclap/imports/optional/08_Intro_ML_Part_2_optional.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L03-O03 · Deployment will predict future months for fields not used in training. The dataset has repeated monthly rows for each field. Which held-out evaluation matches both requirements?</t>
+          <t>L03-O03 · A yield model is trained on fields A–D using data from 2021–2023. We want to predict yields in 2024 for new fields. Which test set best checks this?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Randomly shuffle individual rows so the same fields and future dates can appear in training.</t>
+          <t>2024 records from fields A–D.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Train on earlier data from one group of fields, then evaluate later data from different fields.</t>
+          <t>2024 records from different fields, E–H.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Hold out later months but keep exactly the same fields in training and evaluation.</t>
+          <t>2021–2023 records from different fields, E–H.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Hold out field identities but allow later measurements to enter training before predicting earlier dates.</t>
+          <t>Unused 2021–2023 records from fields A–D, selected at random.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
